--- a/business/rzp-key.xlsx
+++ b/business/rzp-key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{144BB457-93C4-4515-9D9B-DE5A335D392C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D43797-B760-4A1E-9165-EB9B92D927BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9560D08B-2F70-48CF-9125-A450C9E469D7}"/>
   </bookViews>
@@ -28,10 +28,10 @@
     <t>key_secret</t>
   </si>
   <si>
-    <t>rzp_test_Sq8Br8u1sLkS9Q</t>
+    <t>rzp_test_Sq9oM9WyRyKjHo</t>
   </si>
   <si>
-    <t>V8URkUtZKN4EgJKKE94kBJMA</t>
+    <t>cgtbPh1qLSZa7MGghOxen8Sc</t>
   </si>
 </sst>
 </file>
